--- a/markets/prospects/Qatar_Fashion_Prospects.xlsx
+++ b/markets/prospects/Qatar_Fashion_Prospects.xlsx
@@ -519,12 +519,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Company Phone Numbers (comma separated)</t>
+          <t>Company Phone Numbers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Company Emails (comma separated; marketing/sales/business only)</t>
+          <t>Company Emails</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">

--- a/markets/prospects/Qatar_Fashion_Prospects.xlsx
+++ b/markets/prospects/Qatar_Fashion_Prospects.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Prospects'!$A$1:$J$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing, Darwish Holding (owner of Fifty One East)</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+97444104327</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>sustainability@dolcegabbana.com</t>
+          <t>sustainability@dolcegabbana.com, info@everfashion.com.qa</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dina Amr Helmy</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Director, Ever Fashion Luxury Group (Qatar operator)</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+442033186032, +16468891895</t>
+          <t>+442033186032, +16468891895, +97444104327</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@everfashion.com.qa</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dina Amr Helmy</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Director, Ever Fashion Luxury Group (Qatar operator)</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>+97444278436</t>
+          <t>+97444278436, +97444104327</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@everfashion.com.qa</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dina Amr Helmy</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Director, Ever Fashion Luxury Group (Qatar operator)</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sanja Gorgieva</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Brand Manager - Ted Baker (MENA), Al-Futtaim</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3710,22 +3710,22 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Calvin Klein</t>
+          <t>Luxury Shopping in Qatar</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>https://www.calvinklein.qa/</t>
+          <t>https://51east.com/</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Michelle Hirst</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, South-East Hub (SE Europe, MEA, CIS) - Calvin Klein &amp; Tommy Hilfiger, PVH</t>
+          <t>Head of Marketing, Darwish Holding (owner of Fifty One East)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -3740,29 +3740,29 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/michelle-hirst</t>
+          <t>https://linkedin.com/in/anis-aramouni-3254216</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Calvin Klein</t>
+          <t>Luxury Shopping in Qatar</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.calvinklein.qa/</t>
+          <t>https://51east.com/</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Rohan Balchandani</t>
+          <t>Bader Al-Darwish</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Manager E-Commerce &amp; Customer Experience (CK &amp; Tommy Hilfiger D2C sites, SE Europe/Middle East/Africa), PVH</t>
+          <t>Chairman and Managing Director, Fifty One East / Darwish Holding</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3775,31 +3775,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/rohanbalchandani</t>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Massimo Dutti Qatar (Azadea)</t>
+          <t>Luxury Shopping in Qatar</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/qa/</t>
+          <t>https://51east.com/</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Ahmad Karaki</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Multi-brands Marketing Manager, 51 East</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -3814,29 +3814,29 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://linkedin.com/in/ahmad-karaki-42979064</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Massimo Dutti Qatar (Azadea)</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/qa/</t>
+          <t>https://www.calvinklein.qa/</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Michelle Hirst</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Director of Ecommerce, South-East Hub (SE Europe, MEA, CIS) - Calvin Klein &amp; Tommy Hilfiger, PVH</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3851,29 +3851,29 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://linkedin.com/in/michelle-hirst</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Stradivarius Qatar (Azadea)</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/qa/</t>
+          <t>https://www.calvinklein.qa/</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Rohan Balchandani</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Manager E-Commerce &amp; Customer Experience (CK &amp; Tommy Hilfiger D2C sites, SE Europe/Middle East/Africa), PVH</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -3888,29 +3888,29 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://linkedin.com/in/rohanbalchandani</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Stradivarius Qatar (Azadea)</t>
+          <t>Massimo Dutti Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/qa/</t>
+          <t>https://www.massimodutti.com/qa/</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3925,29 +3925,29 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>American Eagle Qatar (Alshaya)</t>
+          <t>Massimo Dutti Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.com.qa/</t>
+          <t>https://www.massimodutti.com/qa/</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -3962,29 +3962,29 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>American Eagle Qatar (Alshaya)</t>
+          <t>Stradivarius Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.com.qa/</t>
+          <t>https://www.stradivarius.com/qa/</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3999,29 +3999,29 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Oysho Qatar (Azadea)</t>
+          <t>Stradivarius Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/qa/</t>
+          <t>https://www.stradivarius.com/qa/</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -4036,29 +4036,29 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Oysho Qatar (Azadea)</t>
+          <t>American Eagle Qatar (Alshaya)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/qa/</t>
+          <t>https://www.americaneagle.com.qa/</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4073,29 +4073,29 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Matalan Qatar</t>
+          <t>American Eagle Qatar (Alshaya)</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>https://www.matalanme.com/qa_ar</t>
+          <t>https://www.americaneagle.com.qa/</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Hasit Kakkad</t>
+          <t>Maëlle Mandjee (Basselot)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>General Manager, BTC Fashion (Matalan, Miniso, Superdry, Balabala franchise operator)</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -4110,29 +4110,29 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/hasit-kakkad-1a47a725</t>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
+          <t>Oysho Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>https://qa.alnasser.net/</t>
+          <t>https://www.oysho.com/qa/</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Fayssal Jilani</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Group Ecommerce Manager, Al Nasser (Faisal Al Rasheed Group; KW, QA, BH, KSA, IQ, EG, PK)</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4147,29 +4147,29 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fayssaljilani</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
+          <t>Oysho Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>https://qa.alnasser.net/</t>
+          <t>https://www.oysho.com/qa/</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Yousef Faisal Al Rashid</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Group CEO, Al Nasser</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -4182,31 +4182,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>VogaCloset</t>
+          <t>Matalan Qatar</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>https://vogacloset.com/qatar/</t>
+          <t>https://www.matalanme.com/qa_ar</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Hanin Hamarneh</t>
+          <t>Hasit Kakkad</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, VogaCloset</t>
+          <t>General Manager, BTC Fashion (Matalan, Miniso, Superdry, Balabala franchise operator)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4221,29 +4221,29 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hanin-hamarneh-05813a1a</t>
+          <t>https://linkedin.com/in/hasit-kakkad-1a47a725</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Riva Fashion</t>
+          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>https://www.rivafashion.com/en-qa/</t>
+          <t>https://qa.alnasser.net/</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Haifa Zawahreh</t>
+          <t>Fayssal Jilani</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Head of Digital Growth, Armada Retail Concept (owner of RIVA)</t>
+          <t>Group Ecommerce Manager, Al Nasser (Faisal Al Rasheed Group; KW, QA, BH, KSA, IQ, EG, PK)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -4256,31 +4256,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fayssaljilani</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Muji</t>
+          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>https://www.muji.qa/en/</t>
+          <t>https://qa.alnasser.net/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Yousef Faisal Al Rashid</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Group CEO, Al Nasser</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4293,31 +4293,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Muji</t>
+          <t>VogaCloset</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>https://www.muji.qa/en/</t>
+          <t>https://vogacloset.com/qatar/</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Farid Khan</t>
+          <t>Hanin Hamarneh</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Operations Manager Qatar (NEXT, MUJI, Claire's, Disney), Alshaya Group</t>
+          <t>Founder &amp; CEO, VogaCloset</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -4332,29 +4332,29 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/farid-khan-b86b8524</t>
+          <t>https://www.linkedin.com/in/hanin-hamarneh-05813a1a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Dolce &amp; Gabbana</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>https://www.chloe.com/qa/</t>
+          <t>https://www.dolcegabbana.com/en-qa/</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nagi Azar</t>
+          <t>Dina Amr Helmy</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Commercial Manager Middle East (Retail &amp; Wholesale), Chloé - Richemont</t>
+          <t>Marketing Director, Ever Fashion Luxury Group (Qatar franchisee/operator)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4369,29 +4369,29 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nagi-azar-a1b88599</t>
+          <t>https://linkedin.com/in/dina-amr-helmy-42009484</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>Dolce &amp; Gabbana</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>https://www.gymshark.qa/</t>
+          <t>https://www.dolcegabbana.com/en-qa/</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Sumit Srivastava</t>
+          <t>Feras Al Yasin</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+          <t>Founder / Managing Partner, Ever Fashion Luxury Group</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -4404,31 +4404,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>Dolce &amp; Gabbana</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>https://www.gymshark.qa/</t>
+          <t>https://www.dolcegabbana.com/en-qa/</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pragya Singh</t>
+          <t>Peter Farah</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager (Mamas &amp; Papas, Gymshark, Gap), Al Tayer Group</t>
+          <t>Country Manager / Retail Director, Ever Fashion Luxury Group</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4443,49 +4443,530 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/pragya-singh-aa428b29</t>
+          <t>https://linkedin.com/in/peter-farah-b24318177</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>Riva Fashion</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.rivafashion.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Haifa Zawahreh</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Head of Digital Growth, Armada Retail Concept (owner of RIVA)</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Balenciaga Qatar</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.balenciaga.com/en-qa</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Dina Amr Helmy</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Director, Ever Fashion Luxury Group (Qatar franchisee/operator)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dina-amr-helmy-42009484</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Balenciaga Qatar</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.balenciaga.com/en-qa</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Feras Al Yasin</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Founder / Managing Partner, Ever Fashion Luxury Group</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Balenciaga Qatar</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.balenciaga.com/en-qa</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Peter Farah</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Country Manager / Retail Director, Ever Fashion Luxury Group</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/peter-farah-b24318177</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Valentino</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.valentino.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Dina Amr Helmy</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Director, Ever Fashion Luxury Group (Qatar franchisee/operator)</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dina-amr-helmy-42009484</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Valentino</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valentino.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Feras Al Yasin</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Founder / Managing Partner, Ever Fashion Luxury Group</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Valentino</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.valentino.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Peter Farah</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Country Manager / Retail Director, Ever Fashion Luxury Group</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/peter-farah-b24318177</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Muji</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.muji.qa/en/</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Rob Silsbury</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Muji</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.muji.qa/en/</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Farid Khan</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Operations Manager Qatar (NEXT, MUJI, Claire's, Disney), Alshaya Group</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/farid-khan-b86b8524</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Chloe</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chloe.com/qa/</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Nagi Azar</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager Middle East (Retail &amp; Wholesale), Chloé - Richemont</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nagi-azar-a1b88599</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Ted Baker QAT</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tedbaker.qa/</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Sanja Gorgieva</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Regional Brand Manager - Ted Baker (MENA), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sanja-gorgieva-b912a087</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>Gymshark</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>https://www.gymshark.qa/</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Sumit Srivastava</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.gymshark.qa/</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Pragya Singh</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager (Mamas &amp; Papas, Gymshark, Gap), Al Tayer Group</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/pragya-singh-aa428b29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gymshark.qa/</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Awatef Airan</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Head of Product (Digital), Al Tayer Retail - incl. Gymshark</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/awatef-airan-29708a114</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G68"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -4556,43 +5037,65 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
